--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -293,6 +293,61 @@
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Template</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Name the factor as the team says it out loud. It must be something you can actually set to either level for the whole run — if you cannot control it, it is noise to block or stratify, not a factor.</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>The level you run today. Keep one arm at current practice so the experiment still tells you whether changing anything was worth it.</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>The level you are testing. Push it far enough to move the response — a timid high level is the most common reason a DOE returns nothing.</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>Name the factor as the team says it out loud. It must be something you can actually set to either level for the whole run — if you cannot control it, it is noise to block or stratify, not a factor.</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <t>The level you run today. Keep one arm at current practice so the experiment still tells you whether changing anything was worth it.</t>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <t>The level you are testing. Push it far enough to move the response — a timid high level is the most common reason a DOE returns nothing.</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>Name the factor as the team says it out loud. It must be something you can actually set to either level for the whole run — if you cannot control it, it is noise to block or stratify, not a factor.</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>The level you run today. Keep one arm at current practice so the experiment still tells you whether changing anything was worth it.</t>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0">
+      <text>
+        <t>The level you are testing. Push it far enough to move the response — a timid high level is the most common reason a DOE returns nothing.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -810,7 +865,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Factor @</t>
+          <t>Factor A</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -844,7 +899,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Factor A</t>
+          <t>Factor B</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -878,7 +933,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Factor B</t>
+          <t>Factor C</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -1342,5 +1397,6 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -242,10 +242,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
             <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'2^3 design'!$A$20:$A$25</f>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -112,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -138,6 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -268,6 +271,40 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Noise floor — the mean interaction, anything smaller is nothing</v>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'2^3 design'!$K$20:$K$25</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -296,6 +333,9 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -361,7 +401,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -817,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -829,6 +869,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1273,6 +1314,11 @@
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Noise floor</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1289,6 +1335,10 @@
           <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
         </is>
       </c>
+      <c r="K20" s="15">
+        <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1305,6 +1355,10 @@
           <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
         </is>
       </c>
+      <c r="K21" s="15">
+        <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -1321,6 +1375,10 @@
           <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
         </is>
       </c>
+      <c r="K22" s="15">
+        <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1337,6 +1395,10 @@
           <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
         </is>
       </c>
+      <c r="K23" s="15">
+        <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1353,6 +1415,10 @@
           <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
         </is>
       </c>
+      <c r="K24" s="15">
+        <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1368,6 +1434,10 @@
         <is>
           <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
         </is>
+      </c>
+      <c r="K25" s="15">
+        <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
+        <v/>
       </c>
     </row>
     <row r="27">

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -244,6 +244,9 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <v>Effect on the response</v>
+          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="1F4E79"/>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -406,7 +406,7 @@
     <from>
       <col>12</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
@@ -1303,6 +1303,7 @@
       </c>
       <c r="I17" s="9" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -1443,6 +1444,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -139,6 +139,9 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1015,27 +1018,30 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>−1 = the low level you set above · +1 = the high level</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="B9" s="11">
+        <f>IF($B$5="","A","A: "&amp;$B$5)</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>IF($B$6="","B","B: "&amp;$B$6)</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>IF($B$7="","C","C: "&amp;$B$7)</f>
+        <v/>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -1054,12 +1060,12 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Response (mean AHT, seconds)</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>What you observed on the day</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1097,11 @@
       <c r="H10" s="14" t="n">
         <v>412</v>
       </c>
-      <c r="I10" s="9" t="n"/>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>Baseline: current routing, $50 authority, no article</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -1121,7 +1131,11 @@
       <c r="H11" s="14" t="n">
         <v>388</v>
       </c>
-      <c r="I11" s="9" t="n"/>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>Skill-based routing alone</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -1151,7 +1165,11 @@
       <c r="H12" s="14" t="n">
         <v>401</v>
       </c>
-      <c r="I12" s="9" t="n"/>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>Higher authority alone — fewer transfers to a supervisor</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -1181,7 +1199,11 @@
       <c r="H13" s="14" t="n">
         <v>372</v>
       </c>
-      <c r="I13" s="9" t="n"/>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>Routing and authority together; the biggest single drop</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -1211,7 +1233,11 @@
       <c r="H14" s="14" t="n">
         <v>395</v>
       </c>
-      <c r="I14" s="9" t="n"/>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>Article shown alone — small effect on its own</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -1241,7 +1267,11 @@
       <c r="H15" s="14" t="n">
         <v>366</v>
       </c>
-      <c r="I15" s="9" t="n"/>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>Routing plus article</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -1271,7 +1301,11 @@
       <c r="H16" s="14" t="n">
         <v>380</v>
       </c>
-      <c r="I16" s="9" t="n"/>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>Authority plus article</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -1301,7 +1335,11 @@
       <c r="H17" s="14" t="n">
         <v>344</v>
       </c>
-      <c r="I17" s="9" t="n"/>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>All three at the high level. Best result, and the one to confirm.</t>
+        </is>
+      </c>
     </row>
     <row r="18"/>
     <row r="19">
@@ -1336,10 +1374,10 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
-        </is>
-      </c>
-      <c r="K20" s="15">
+          <t>Negative means the HIGH level lowers handle time. Biggest single effect here: skill-based routing takes about 29 seconds off the average.</t>
+        </is>
+      </c>
+      <c r="K20" s="16">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1356,10 +1394,10 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
-        </is>
-      </c>
-      <c r="K21" s="15">
+          <t>Raising the authority limit from $50 to $250 takes off about 16 seconds — fewer calls escalated to a supervisor.</t>
+        </is>
+      </c>
+      <c r="K21" s="16">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1376,10 +1414,10 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
-        </is>
-      </c>
-      <c r="K22" s="15">
+          <t>Showing the article takes off about 22 seconds.</t>
+        </is>
+      </c>
+      <c r="K22" s="16">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1396,10 +1434,10 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
-        </is>
-      </c>
-      <c r="K23" s="15">
+          <t>Routing and authority together. Small against the main effects, so the two can be decided independently.</t>
+        </is>
+      </c>
+      <c r="K23" s="16">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1416,10 +1454,10 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
-        </is>
-      </c>
-      <c r="K24" s="15">
+          <t>Routing and article together. Also small.</t>
+        </is>
+      </c>
+      <c r="K24" s="16">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1436,10 +1474,10 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Bigger absolute value = bigger effect. A large interaction means the two factors cannot be set independently.</t>
-        </is>
-      </c>
-      <c r="K25" s="15">
+          <t>Authority and article together. Also small — which is the useful finding: none of these has to be rolled out as a package.</t>
+        </is>
+      </c>
+      <c r="K25" s="16">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1453,10 +1491,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="E24:I24"/>
+    <mergeCell ref="B8:G8"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="E23:I23"/>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -130,6 +130,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1018,52 +1021,52 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>−1 = the low level you set above · +1 = the high level</t>
+    <row r="8" ht="24" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>−1 = the low level you set above · +1 = the high level  ·  Key: AB, AC, BC = interaction columns: the product of two factor columns, +1 or -1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="12">
         <f>IF($B$5="","A","A: "&amp;$B$5)</f>
         <v/>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <f>IF($B$6="","B","B: "&amp;$B$6)</f>
         <v/>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <f>IF($B$7="","C","C: "&amp;$B$7)</f>
         <v/>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>Response (mean AHT, seconds)</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>What you observed on the day</t>
         </is>
@@ -1073,31 +1076,31 @@
       <c r="A10" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="14">
         <f>B10*C10</f>
         <v/>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <f>B10*D10</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="14">
         <f>C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="15" t="n">
         <v>412</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>Baseline: current routing, $50 authority, no article</t>
         </is>
@@ -1107,31 +1110,31 @@
       <c r="A11" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="14">
         <f>B11*C11</f>
         <v/>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>B11*D11</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>C11*D11</f>
         <v/>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="15" t="n">
         <v>388</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>Skill-based routing alone</t>
         </is>
@@ -1141,31 +1144,31 @@
       <c r="A12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="14">
         <f>B12*C12</f>
         <v/>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <f>B12*D12</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <f>C12*D12</f>
         <v/>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="15" t="n">
         <v>401</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>Higher authority alone — fewer transfers to a supervisor</t>
         </is>
@@ -1175,31 +1178,31 @@
       <c r="A13" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="14">
         <f>B13*C13</f>
         <v/>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>B13*D13</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>C13*D13</f>
         <v/>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="15" t="n">
         <v>372</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>Routing and authority together; the biggest single drop</t>
         </is>
@@ -1209,31 +1212,31 @@
       <c r="A14" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="14">
         <f>B14*C14</f>
         <v/>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>B14*D14</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <f>C14*D14</f>
         <v/>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="15" t="n">
         <v>395</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>Article shown alone — small effect on its own</t>
         </is>
@@ -1243,31 +1246,31 @@
       <c r="A15" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="14">
         <f>B15*C15</f>
         <v/>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>B15*D15</f>
         <v/>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <f>C15*D15</f>
         <v/>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="15" t="n">
         <v>366</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>Routing plus article</t>
         </is>
@@ -1277,31 +1280,31 @@
       <c r="A16" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="14">
         <f>B16*C16</f>
         <v/>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f>B16*D16</f>
         <v/>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <f>C16*D16</f>
         <v/>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="15" t="n">
         <v>380</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>Authority plus article</t>
         </is>
@@ -1311,31 +1314,31 @@
       <c r="A17" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="14">
         <f>B17*C17</f>
         <v/>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>B17*D17</f>
         <v/>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <f>C17*D17</f>
         <v/>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="H17" s="15" t="n">
         <v>344</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>All three at the high level. Best result, and the one to confirm.</t>
         </is>
@@ -1368,7 +1371,7 @@
           <t>Effect of A</t>
         </is>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="14">
         <f>SUMPRODUCT(B10:B17,$H$10:$H$17)/4</f>
         <v/>
       </c>
@@ -1377,7 +1380,7 @@
           <t>Negative means the HIGH level lowers handle time. Biggest single effect here: skill-based routing takes about 29 seconds off the average.</t>
         </is>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1388,7 +1391,7 @@
           <t>Effect of B</t>
         </is>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="14">
         <f>SUMPRODUCT(C10:C17,$H$10:$H$17)/4</f>
         <v/>
       </c>
@@ -1397,7 +1400,7 @@
           <t>Raising the authority limit from $50 to $250 takes off about 16 seconds — fewer calls escalated to a supervisor.</t>
         </is>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1408,7 +1411,7 @@
           <t>Effect of C</t>
         </is>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="14">
         <f>SUMPRODUCT(D10:D17,$H$10:$H$17)/4</f>
         <v/>
       </c>
@@ -1417,7 +1420,7 @@
           <t>Showing the article takes off about 22 seconds.</t>
         </is>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1428,7 +1431,7 @@
           <t>Interaction AB</t>
         </is>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="14">
         <f>SUMPRODUCT(E10:E17,$H$10:$H$17)/4</f>
         <v/>
       </c>
@@ -1437,7 +1440,7 @@
           <t>Routing and authority together. Small against the main effects, so the two can be decided independently.</t>
         </is>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1448,7 +1451,7 @@
           <t>Interaction AC</t>
         </is>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="14">
         <f>SUMPRODUCT(F10:F17,$H$10:$H$17)/4</f>
         <v/>
       </c>
@@ -1457,7 +1460,7 @@
           <t>Routing and article together. Also small.</t>
         </is>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1468,7 +1471,7 @@
           <t>Interaction BC</t>
         </is>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="14">
         <f>SUMPRODUCT(G10:G17,$H$10:$H$17)/4</f>
         <v/>
       </c>
@@ -1477,7 +1480,7 @@
           <t>Authority and article together. Also small — which is the useful finding: none of these has to be rolled out as a package.</t>
         </is>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -55,7 +55,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +85,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFAEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -140,10 +145,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -149,6 +149,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1136,10 +1142,10 @@
         <f>C11*D11</f>
         <v/>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="17" t="n">
         <v>388</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>Skill-based routing alone</t>
         </is>
@@ -1170,10 +1176,10 @@
         <f>C12*D12</f>
         <v/>
       </c>
-      <c r="H12" s="15" t="n">
+      <c r="H12" s="17" t="n">
         <v>401</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>Higher authority alone — fewer transfers to a supervisor</t>
         </is>
@@ -1204,10 +1210,10 @@
         <f>C13*D13</f>
         <v/>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="17" t="n">
         <v>372</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>Routing and authority together; the biggest single drop</t>
         </is>
@@ -1238,10 +1244,10 @@
         <f>C14*D14</f>
         <v/>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H14" s="17" t="n">
         <v>395</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>Article shown alone — small effect on its own</t>
         </is>
@@ -1272,10 +1278,10 @@
         <f>C15*D15</f>
         <v/>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H15" s="17" t="n">
         <v>366</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>Routing plus article</t>
         </is>
@@ -1306,10 +1312,10 @@
         <f>C16*D16</f>
         <v/>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H16" s="17" t="n">
         <v>380</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>Authority plus article</t>
         </is>
@@ -1340,10 +1346,10 @@
         <f>C17*D17</f>
         <v/>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="17" t="n">
         <v>344</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>All three at the high level. Best result, and the one to confirm.</t>
         </is>
@@ -1385,7 +1391,7 @@
           <t>Negative means the HIGH level lowers handle time. Biggest single effect here: skill-based routing takes about 29 seconds off the average.</t>
         </is>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="19">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1405,7 +1411,7 @@
           <t>Raising the authority limit from $50 to $250 takes off about 16 seconds — fewer calls escalated to a supervisor.</t>
         </is>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="19">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1425,7 +1431,7 @@
           <t>Showing the article takes off about 22 seconds.</t>
         </is>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="19">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1445,7 +1451,7 @@
           <t>Routing and authority together. Small against the main effects, so the two can be decided independently.</t>
         </is>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="19">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1465,7 +1471,7 @@
           <t>Routing and article together. Also small.</t>
         </is>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="19">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1485,7 +1491,7 @@
           <t>Authority and article together. Also small — which is the useful finding: none of these has to be rolled out as a package.</t>
         </is>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="19">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -149,12 +149,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -772,14 +766,14 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>Green cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example so you can see the expected format. Delete it when you start.</t>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
         </is>
       </c>
     </row>
@@ -1142,10 +1136,10 @@
         <f>C11*D11</f>
         <v/>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="15" t="n">
         <v>388</v>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>Skill-based routing alone</t>
         </is>
@@ -1176,10 +1170,10 @@
         <f>C12*D12</f>
         <v/>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="15" t="n">
         <v>401</v>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>Higher authority alone — fewer transfers to a supervisor</t>
         </is>
@@ -1210,10 +1204,10 @@
         <f>C13*D13</f>
         <v/>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="15" t="n">
         <v>372</v>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>Routing and authority together; the biggest single drop</t>
         </is>
@@ -1244,10 +1238,10 @@
         <f>C14*D14</f>
         <v/>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="15" t="n">
         <v>395</v>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>Article shown alone — small effect on its own</t>
         </is>
@@ -1278,10 +1272,10 @@
         <f>C15*D15</f>
         <v/>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H15" s="15" t="n">
         <v>366</v>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>Routing plus article</t>
         </is>
@@ -1312,10 +1306,10 @@
         <f>C16*D16</f>
         <v/>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H16" s="15" t="n">
         <v>380</v>
       </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>Authority plus article</t>
         </is>
@@ -1346,10 +1340,10 @@
         <f>C17*D17</f>
         <v/>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="15" t="n">
         <v>344</v>
       </c>
-      <c r="I17" s="18" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>All three at the high level. Best result, and the one to confirm.</t>
         </is>
@@ -1391,7 +1385,7 @@
           <t>Negative means the HIGH level lowers handle time. Biggest single effect here: skill-based routing takes about 29 seconds off the average.</t>
         </is>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1411,7 +1405,7 @@
           <t>Raising the authority limit from $50 to $250 takes off about 16 seconds — fewer calls escalated to a supervisor.</t>
         </is>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1431,7 +1425,7 @@
           <t>Showing the article takes off about 22 seconds.</t>
         </is>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1451,7 +1445,7 @@
           <t>Routing and authority together. Small against the main effects, so the two can be decided independently.</t>
         </is>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1471,7 +1465,7 @@
           <t>Routing and article together. Also small.</t>
         </is>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>
@@ -1491,7 +1485,7 @@
           <t>Authority and article together. Also small — which is the useful finding: none of these has to be rolled out as a package.</t>
         </is>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
       </c>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -1029,7 +1029,8 @@
     <row r="8" ht="24" customHeight="1">
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>−1 = the low level you set above · +1 = the high level  ·  Key: AB, AC, BC = interaction columns: the product of two factor columns, +1 or -1</t>
+          <t>−1 = the low level you set above · +1 = the high level  ·  Key:
+• AB, AC, BC = interaction columns: the product of two factor columns, +1 or -1</t>
         </is>
       </c>
     </row>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +53,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -119,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,6 +157,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,7 +423,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>14</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -871,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -884,6 +892,15 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1411,7 +1428,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Effect of C</t>
@@ -1429,6 +1446,12 @@
       <c r="K22" s="17">
         <f>-AVERAGE(ABS($D$23),ABS($D$24),ABS($D$25))</f>
         <v/>
+      </c>
+      <c r="M22" s="18" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Bars are effects, so length is what matters and the sign only tells you which way. Read the interactions beside the main effects: a large interaction means neither factor can be set on its own, and reporting its main effect alone is how a DOE result stops replicating.
+SO:  Set the factors with the long bars and leave the short ones at whatever is cheapest. Where an interaction is large, fix that pair together and confirm with a run at the chosen settings before rolling out.</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1500,7 +1523,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="E24:I24"/>
@@ -1508,6 +1531,7 @@
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="E23:I23"/>
+    <mergeCell ref="M22:U22"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="A23:C23"/>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -774,73 +774,61 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green cells</t>
+          <t>What this is for</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
+          <t>Finding the best combination of settings, and detecting interactions — where two changes together do something neither does alone. One-factor-at-a-time testing cannot see those at all.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>What this is for</t>
+          <t>How to use it</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Finding the best combination of settings, and detecting interactions — where two changes together do something neither does alone. One-factor-at-a-time testing cannot see those at all.</t>
+          <t>Name three factors and their two levels. Run all eight combinations in randomised order and enter the response you measured. The effects table then tells you which factor moved it and by how much.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>How to use it</t>
+          <t>In support</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Name three factors and their two levels. Run all eight combinations in randomised order and enter the response you measured. The effects table then tells you which factor moved it and by how much.</t>
+          <t>Factors are things like routing rule, authority limit, whether an article is shown, script version. The response is handle time, resolution rate or satisfaction.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>In support</t>
+          <t>The trap</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Factors are things like routing rule, authority limit, whether an article is shown, script version. The response is handle time, resolution rate or satisfaction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>The trap</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="2" t="inlineStr">
-        <is>
           <t>Run the design as designed. Dropping the combinations that look silly destroys the balance the whole method depends on and the effects become uninterpretable.</t>
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>

--- a/templates/24-doe-design-matrix.xlsx
+++ b/templates/24-doe-design-matrix.xlsx
@@ -735,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -774,61 +774,73 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>What this is for</t>
+          <t>Green cells</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Finding the best combination of settings, and detecting interactions — where two changes together do something neither does alone. One-factor-at-a-time testing cannot see those at all.</t>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>How to use it</t>
+          <t>What this is for</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Name three factors and their two levels. Run all eight combinations in randomised order and enter the response you measured. The effects table then tells you which factor moved it and by how much.</t>
+          <t>Finding the best combination of settings, and detecting interactions — where two changes together do something neither does alone. One-factor-at-a-time testing cannot see those at all.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>In support</t>
+          <t>How to use it</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Factors are things like routing rule, authority limit, whether an article is shown, script version. The response is handle time, resolution rate or satisfaction.</t>
+          <t>Name three factors and their two levels. Run all eight combinations in randomised order and enter the response you measured. The effects table then tells you which factor moved it and by how much.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>The trap</t>
+          <t>In support</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>Factors are things like routing rule, authority limit, whether an article is shown, script version. The response is handle time, resolution rate or satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>The trap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>Run the design as designed. Dropping the combinations that look silly destroys the balance the whole method depends on and the effects become uninterpretable.</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
@@ -854,6 +866,8 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
